--- a/docs/Mapping_casi_uso/cittadinanza/Citt_047.xlsx
+++ b/docs/Mapping_casi_uso/cittadinanza/Citt_047.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="75">
   <si>
     <t>Sezione</t>
   </si>
@@ -204,6 +204,39 @@
   </si>
   <si>
     <t>dettaglioRettifica</t>
+  </si>
+  <si>
+    <t>Atto collegato di Cittadinanza</t>
+  </si>
+  <si>
+    <t>evento.eventoCollegatoCittadinanza</t>
+  </si>
+  <si>
+    <t>opzionale</t>
+  </si>
+  <si>
+    <t>Tipo evento</t>
+  </si>
+  <si>
+    <t>idtipocontenuto</t>
+  </si>
+  <si>
+    <t>Parte</t>
+  </si>
+  <si>
+    <t>parte</t>
+  </si>
+  <si>
+    <t>Serie</t>
+  </si>
+  <si>
+    <t>serie</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>volume</t>
   </si>
 </sst>
 </file>
@@ -262,10 +295,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="19.31640625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="27.4296875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="33.30859375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="33.921875" customWidth="true" bestFit="true"/>
@@ -849,6 +882,305 @@
         <v>19</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
